--- a/madaporc_suivi_dynamique_plutot.xlsx
+++ b/madaporc_suivi_dynamique_plutot.xlsx
@@ -2355,7 +2355,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ABEC7A2D-6428-4639-8FE6-708D74EDB67E}</x14:id>
+          <x14:id>{60FE68CE-882F-4BA5-B0FE-7072EF29D238}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2371,7 +2371,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ABEC7A2D-6428-4639-8FE6-708D74EDB67E}">
+          <x14:cfRule type="dataBar" id="{60FE68CE-882F-4BA5-B0FE-7072EF29D238}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3180,7 +3180,7 @@
         <v>409</v>
       </c>
       <c r="D3" s="41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>410</v>

--- a/madaporc_suivi_dynamique_plutot.xlsx
+++ b/madaporc_suivi_dynamique_plutot.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Récapitulatif" sheetId="1" state="visible" r:id="rId3"/>
@@ -20,6 +20,7 @@
     <sheet name="MANDRESY" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Transversal &amp; Jury" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Sheet12" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Sheet13" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="SUM" vbProcedure="false">MANDRESY!$F$17</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="438">
   <si>
     <t xml:space="preserve">MADAPORC — Suivi des tâches &amp; fonctions par membre</t>
   </si>
@@ -321,6 +322,9 @@
     <t xml:space="preserve">TOTAL (min)</t>
   </si>
   <si>
+    <t xml:space="preserve">Dav</t>
+  </si>
+  <si>
     <t xml:space="preserve">Binôme 1 (avec Miaro)   ·   Branche(s) : dev_davida, dev-Miaro-Davida</t>
   </si>
   <si>
@@ -444,6 +448,9 @@
     <t xml:space="preserve">Liste + formulaire clients</t>
   </si>
   <si>
+    <t xml:space="preserve">y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Binôme 2 (avec Nomena)   ·   Branche(s) : dev_fanilo, dev_fanilo_nomena</t>
   </si>
   <si>
@@ -720,9 +727,6 @@
     <t xml:space="preserve">byModule · byStatut · orderByDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Présent</t>
-  </si>
-  <si>
     <t xml:space="preserve">model/ImportExport.java</t>
   </si>
   <si>
@@ -1306,6 +1310,45 @@
   </si>
   <si>
     <t xml:space="preserve">Irina </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temps(min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temps(heures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tarif horaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dev Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fanilo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarobidy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tsanta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mickaella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah</t>
   </si>
 </sst>
 </file>
@@ -1319,11 +1362,11 @@
     <numFmt numFmtId="167" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
     <numFmt numFmtId="169" formatCode="0\ %"/>
-    <numFmt numFmtId="170" formatCode="General"/>
-    <numFmt numFmtId="171" formatCode="0%"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="0"/>
-    <numFmt numFmtId="174" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="170" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="173" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="174" formatCode="#,##0"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -1561,7 +1604,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1610,7 +1653,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1618,11 +1669,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="8" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1630,19 +1681,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1662,7 +1705,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1686,7 +1729,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1698,15 +1741,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="8" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="8" fillId="8" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1718,7 +1753,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1730,12 +1773,16 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1961,7 +2008,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
@@ -2171,11 +2218,11 @@
       </c>
       <c r="D11" s="12" t="str">
         <f aca="false">COUNTIF(TSANTA!$G$7:$G$24,"Terminé")&amp;"/"&amp;COUNT(TSANTA!$A$7:$A$24)</f>
-        <v>15/18</v>
+        <v>18/18</v>
       </c>
       <c r="E11" s="13" t="n">
-        <f aca="false">IFERROR((SUMIF(TSANTA!$G$7:$G$24,"Terminé",TSANTA!$F$7:$F$24)+0.5*SUMIF(TSANTA!$G$7:$G$24,"En cours",TSANTA!$F$7:$F$24))/SUM(TSANTA!$F$7:$F$24),0)</f>
-        <v>0.656565656565657</v>
+        <f aca="false">E10</f>
+        <v>1</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">SUM(TSANTA!$F$7:$F$24)/60</f>
@@ -2183,11 +2230,11 @@
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">(SUMIF(TSANTA!$G$7:$G$24,"Terminé",TSANTA!$F$7:$F$24)+0.5*SUMIF(TSANTA!$G$7:$G$24,"En cours",TSANTA!$F$7:$F$24))/60</f>
-        <v>10.8333333333333</v>
+        <v>16.5</v>
       </c>
       <c r="H11" s="15" t="n">
-        <f aca="false">(SUMIF(TSANTA!$G$7:$G$24,"Pas fini",TSANTA!$F$7:$F$24)+0.5*SUMIF(TSANTA!$G$7:$G$24,"En cours",TSANTA!$F$7:$F$24))/60</f>
-        <v>5.66666666666667</v>
+        <f aca="false">H10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2315,10 +2362,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="str">
-        <f aca="false">"⚠ Le plus en retard : "&amp;INDEX($A$7:$A$15,MATCH(MAX($H$7:$H$15),$H$7:$H$15,0))&amp;" ("&amp;TEXT(MAX($H$7:$H$15),"0.0")&amp;" h restantes)"</f>
-        <v>⚠ Le plus en retard : TSANTA — Tsanta Finaritra (Noahmathieu) (5,7 h restantes)</v>
-      </c>
+      <c r="A17" s="20"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -2355,7 +2399,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60FE68CE-882F-4BA5-B0FE-7072EF29D238}</x14:id>
+          <x14:id>{EDBD3C1D-6EC1-4050-90A6-627443F31762}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2371,7 +2415,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60FE68CE-882F-4BA5-B0FE-7072EF29D238}">
+          <x14:cfRule type="dataBar" id="{EDBD3C1D-6EC1-4050-90A6-627443F31762}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -2393,7 +2437,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.44"/>
@@ -2419,7 +2463,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -2454,7 +2498,7 @@
       <c r="G4" s="25"/>
       <c r="H4" s="25"/>
     </row>
-    <row r="7" s="37" customFormat="true" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" s="35" customFormat="true" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
         <v>42</v>
       </c>
@@ -2485,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="30"/>
@@ -2508,13 +2552,13 @@
         <v>79</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>15</v>
@@ -2532,13 +2576,13 @@
         <v>79</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>15</v>
@@ -2556,13 +2600,13 @@
         <v>79</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>10</v>
@@ -2580,13 +2624,13 @@
         <v>79</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>10</v>
@@ -2607,10 +2651,10 @@
         <v>89</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>30</v>
@@ -2631,10 +2675,10 @@
         <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>150</v>
@@ -2658,7 +2702,7 @@
         <v>65</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>25</v>
@@ -2673,16 +2717,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>40</v>
@@ -2731,7 +2775,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -2742,14 +2786,14 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="A1" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
@@ -2777,13 +2821,13 @@
         <v>42</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>48</v>
@@ -2800,19 +2844,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G5" s="31" t="n">
         <v>120</v>
@@ -2823,19 +2867,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>372</v>
       </c>
       <c r="G6" s="31" t="n">
         <v>120</v>
@@ -2846,19 +2890,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G7" s="31" t="n">
         <v>120</v>
@@ -2869,13 +2913,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E8" s="32" t="s">
         <v>2</v>
@@ -2890,15 +2934,15 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="E9" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="E9" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="11"/>
@@ -2911,15 +2955,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="E10" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="E10" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F10" s="11"/>
@@ -2932,15 +2976,15 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="11"/>
@@ -2953,13 +2997,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>2</v>
@@ -2974,15 +3018,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="E13" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="E13" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="11"/>
@@ -2995,19 +3039,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G14" s="31" t="n">
         <v>30</v>
@@ -3018,19 +3062,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="E15" s="35" t="s">
+        <v>393</v>
+      </c>
+      <c r="E15" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G15" s="31" t="n">
         <v>30</v>
@@ -3041,19 +3085,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="E16" s="35" t="s">
+        <v>396</v>
+      </c>
+      <c r="E16" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G16" s="31" t="n">
         <v>30</v>
@@ -3064,19 +3108,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="E17" s="35" t="s">
+        <v>399</v>
+      </c>
+      <c r="E17" s="37" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G17" s="31" t="n">
         <v>30</v>
@@ -3087,19 +3131,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="E18" s="36" t="s">
+        <v>403</v>
+      </c>
+      <c r="E18" s="38" t="s">
         <v>3</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G18" s="31" t="n">
         <v>120</v>
@@ -3150,7 +3194,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="C2:G11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="40" width="30.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="40" width="32.82"/>
@@ -3160,33 +3204,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="40" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D2" s="40" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E2" s="40" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="40" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D3" s="41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G3" s="41" t="n">
         <v>1</v>
@@ -3194,16 +3238,16 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="40" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E4" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G4" s="41" t="n">
         <v>-3</v>
@@ -3211,7 +3255,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="40" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D5" s="41" t="n">
         <v>0</v>
@@ -3220,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G5" s="41" t="n">
         <v>1</v>
@@ -3228,7 +3272,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="40" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D6" s="41" t="n">
         <v>0</v>
@@ -3237,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G6" s="41" t="n">
         <v>1</v>
@@ -3245,7 +3289,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="40" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D7" s="41" t="n">
         <v>2</v>
@@ -3254,7 +3298,7 @@
         <v>46193</v>
       </c>
       <c r="F7" s="43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G7" s="41" t="n">
         <v>1</v>
@@ -3262,7 +3306,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="40" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>1</v>
@@ -3271,7 +3315,7 @@
         <v>46186</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G8" s="41" t="n">
         <v>1</v>
@@ -3279,7 +3323,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="40" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D9" s="41" t="n">
         <v>1</v>
@@ -3288,7 +3332,7 @@
         <v>46207</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G9" s="41" t="n">
         <v>1</v>
@@ -3296,7 +3340,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="40" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D10" s="41" t="n">
         <v>0</v>
@@ -3305,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G10" s="41" t="n">
         <v>1</v>
@@ -3313,19 +3357,244 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="40" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E11" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G11" s="41" t="n">
         <v>-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.19"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>440</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F2" s="44" t="n">
+        <f aca="false">(C2/60)*E2</f>
+        <v>62333.3333333333</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <f aca="false">B2</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>995</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F3" s="44" t="n">
+        <f aca="false">(C3/60)*E3</f>
+        <v>140958.333333333</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B4" s="0" t="str">
+        <f aca="false">B3</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F4" s="44" t="n">
+        <f aca="false">(C4/60)*E4</f>
+        <v>198333.333333333</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="B5" s="0" t="str">
+        <f aca="false">B4</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>750</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F5" s="44" t="n">
+        <f aca="false">(C5/60)*E5</f>
+        <v>106250</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B6" s="0" t="str">
+        <f aca="false">B5</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>990</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F6" s="44" t="n">
+        <f aca="false">(C6/60)*E6</f>
+        <v>140250</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" s="0" t="str">
+        <f aca="false">B6</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>760</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F7" s="44" t="n">
+        <f aca="false">(C7/60)*E7</f>
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="B8" s="0" t="str">
+        <f aca="false">B7</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>840</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F8" s="44" t="n">
+        <f aca="false">(C8/60)*E8</f>
+        <v>119000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B9" s="0" t="str">
+        <f aca="false">B8</f>
+        <v>Dev Junior</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <f aca="false">(C9/60)*E9</f>
+        <v>144500</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="44" t="n">
+        <f aca="false">SUM(F2:F9)</f>
+        <v>1291625</v>
       </c>
     </row>
   </sheetData>
@@ -3345,7 +3614,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -3902,7 +4171,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -3916,7 +4185,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -3928,7 +4197,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -4000,10 +4269,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -4024,10 +4293,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -4048,10 +4317,10 @@
         <v>80</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>30</v>
@@ -4072,10 +4341,10 @@
         <v>80</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>30</v>
@@ -4096,10 +4365,10 @@
         <v>80</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>30</v>
@@ -4120,10 +4389,10 @@
         <v>80</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>30</v>
@@ -4144,10 +4413,10 @@
         <v>80</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>30</v>
@@ -4168,10 +4437,10 @@
         <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>30</v>
@@ -4192,10 +4461,10 @@
         <v>85</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>30</v>
@@ -4216,10 +4485,10 @@
         <v>85</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>30</v>
@@ -4240,10 +4509,10 @@
         <v>85</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>180</v>
@@ -4264,10 +4533,10 @@
         <v>89</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>30</v>
@@ -4285,13 +4554,13 @@
         <v>50</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>60</v>
@@ -4312,10 +4581,10 @@
         <v>70</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>60</v>
@@ -4336,10 +4605,10 @@
         <v>80</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>30</v>
@@ -4360,10 +4629,10 @@
         <v>80</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F22" s="31" t="n">
         <v>30</v>
@@ -4384,10 +4653,10 @@
         <v>80</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>30</v>
@@ -4408,10 +4677,10 @@
         <v>80</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>30</v>
@@ -4420,7 +4689,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4434,10 +4703,10 @@
         <v>85</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F25" s="31" t="n">
         <v>150</v>
@@ -4458,10 +4727,10 @@
         <v>89</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F26" s="31" t="n">
         <v>30</v>
@@ -4479,13 +4748,13 @@
         <v>79</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F27" s="31" t="n">
         <v>15</v>
@@ -4503,13 +4772,13 @@
         <v>79</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F28" s="31" t="n">
         <v>10</v>
@@ -4530,10 +4799,10 @@
         <v>70</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F29" s="31" t="n">
         <v>40</v>
@@ -4581,7 +4850,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -4595,7 +4864,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -4607,7 +4876,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -4679,10 +4948,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -4703,10 +4972,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -4727,10 +4996,10 @@
         <v>80</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>30</v>
@@ -4751,10 +5020,10 @@
         <v>80</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>30</v>
@@ -4775,10 +5044,10 @@
         <v>80</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>30</v>
@@ -4799,10 +5068,10 @@
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>240</v>
@@ -4823,10 +5092,10 @@
         <v>89</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>90</v>
@@ -4844,13 +5113,13 @@
         <v>50</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>75</v>
@@ -4871,10 +5140,10 @@
         <v>70</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>60</v>
@@ -4895,10 +5164,10 @@
         <v>80</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>30</v>
@@ -4919,10 +5188,10 @@
         <v>80</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>30</v>
@@ -4943,10 +5212,10 @@
         <v>85</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>150</v>
@@ -4967,10 +5236,10 @@
         <v>89</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>15</v>
@@ -4988,13 +5257,13 @@
         <v>50</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>45</v>
@@ -5015,10 +5284,10 @@
         <v>80</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>180</v>
@@ -5027,7 +5296,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5041,10 +5310,10 @@
         <v>85</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F22" s="31" t="n">
         <v>180</v>
@@ -5053,7 +5322,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5067,10 +5336,10 @@
         <v>89</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>45</v>
@@ -5079,7 +5348,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5090,13 +5359,13 @@
         <v>79</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>30</v>
@@ -5105,7 +5374,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5116,13 +5385,13 @@
         <v>79</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F25" s="31" t="n">
         <v>20</v>
@@ -5131,7 +5400,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5145,10 +5414,10 @@
         <v>70</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F26" s="31" t="n">
         <v>60</v>
@@ -5196,7 +5465,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -5222,7 +5491,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -5294,10 +5563,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -5318,10 +5587,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -5342,10 +5611,10 @@
         <v>85</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>90</v>
@@ -5366,10 +5635,10 @@
         <v>89</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>15</v>
@@ -5387,13 +5656,13 @@
         <v>50</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>45</v>
@@ -5414,10 +5683,10 @@
         <v>80</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>90</v>
@@ -5438,10 +5707,10 @@
         <v>80</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>90</v>
@@ -5462,10 +5731,10 @@
         <v>80</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>90</v>
@@ -5486,10 +5755,10 @@
         <v>85</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>30</v>
@@ -5510,10 +5779,10 @@
         <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>15</v>
@@ -5531,13 +5800,13 @@
         <v>50</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>75</v>
@@ -5555,13 +5824,13 @@
         <v>50</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>30</v>
@@ -5582,10 +5851,10 @@
         <v>70</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>120</v>
@@ -5633,7 +5902,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -5659,7 +5928,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -5684,7 +5953,7 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="str">
         <f aca="false">"Avancement : "&amp;COUNTIF($G$7:$G$24,"Terminé")&amp;"/"&amp;COUNT($A$7:$A$24)&amp;" fonctions · "&amp;TEXT(IFERROR((SUMIF($G$7:$G$24,"Terminé",$F$7:$F$24)+0.5*SUMIF($G$7:$G$24,"En cours",$F$7:$F$24))/SUM($F$7:$F$24),0),"0%")&amp;"   ·   Durée totale estimée : "&amp;TEXT(SUM($F$7:$F$24)/60,"0.0")&amp;" h"&amp;"   ·   Heures faites : "&amp;TEXT((SUMIF($G$7:$G$24,"Terminé",$F$7:$F$24)+0.5*SUMIF($G$7:$G$24,"En cours",$F$7:$F$24))/60,"0.0")&amp;" h"&amp;"   ·   Heures restantes : "&amp;TEXT((SUMIF($G$7:$G$24,"Pas fini",$F$7:$F$24)+0.5*SUMIF($G$7:$G$24,"En cours",$F$7:$F$24))/60,"0.0")&amp;" h"</f>
-        <v>Avancement : 15/18 fonctions · 66%   ·   Durée totale estimée : 16,5 h   ·   Heures faites : 10,8 h   ·   Heures restantes : 5,7 h</v>
+        <v>Avancement : 18/18 fonctions · 100%   ·   Durée totale estimée : 16,5 h   ·   Heures faites : 16,5 h   ·   Heures restantes : 0,0 h</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -5731,10 +6000,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -5755,10 +6024,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -5779,10 +6048,10 @@
         <v>80</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>30</v>
@@ -5803,10 +6072,10 @@
         <v>85</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>30</v>
@@ -5827,10 +6096,10 @@
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>30</v>
@@ -5851,10 +6120,10 @@
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>30</v>
@@ -5875,10 +6144,10 @@
         <v>85</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>90</v>
@@ -5899,10 +6168,10 @@
         <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>30</v>
@@ -5923,10 +6192,10 @@
         <v>85</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>90</v>
@@ -5947,10 +6216,10 @@
         <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>45</v>
@@ -5971,10 +6240,10 @@
         <v>89</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>15</v>
@@ -5992,13 +6261,13 @@
         <v>50</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>90</v>
@@ -6019,20 +6288,18 @@
         <v>80</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>180</v>
       </c>
-      <c r="G19" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>163</v>
-      </c>
+      <c r="G19" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
@@ -6045,20 +6312,18 @@
         <v>85</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="G20" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>163</v>
-      </c>
+      <c r="G20" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
@@ -6071,10 +6336,10 @@
         <v>89</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>45</v>
@@ -6082,9 +6347,7 @@
       <c r="G21" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="11" t="s">
-        <v>228</v>
-      </c>
+      <c r="H21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
@@ -6094,13 +6357,13 @@
         <v>79</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F22" s="31" t="n">
         <v>15</v>
@@ -6108,9 +6371,7 @@
       <c r="G22" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="11" t="s">
-        <v>228</v>
-      </c>
+      <c r="H22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
@@ -6120,23 +6381,21 @@
         <v>79</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="G23" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="G23" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
@@ -6149,10 +6408,10 @@
         <v>70</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>40</v>
@@ -6200,7 +6459,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -6226,7 +6485,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -6298,10 +6557,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -6322,10 +6581,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -6349,10 +6608,10 @@
         <v>80</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>30</v>
@@ -6373,10 +6632,10 @@
         <v>80</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>30</v>
@@ -6385,7 +6644,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6399,10 +6658,10 @@
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>30</v>
@@ -6423,10 +6682,10 @@
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>30</v>
@@ -6447,10 +6706,10 @@
         <v>85</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>30</v>
@@ -6471,10 +6730,10 @@
         <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>30</v>
@@ -6495,10 +6754,10 @@
         <v>85</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>30</v>
@@ -6507,7 +6766,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6521,10 +6780,10 @@
         <v>85</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>30</v>
@@ -6533,7 +6792,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6547,10 +6806,10 @@
         <v>85</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>30</v>
@@ -6559,7 +6818,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6573,10 +6832,10 @@
         <v>85</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>30</v>
@@ -6585,7 +6844,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6599,10 +6858,10 @@
         <v>85</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>30</v>
@@ -6611,7 +6870,7 @@
         <v>2</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6625,10 +6884,10 @@
         <v>85</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>30</v>
@@ -6637,7 +6896,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6648,13 +6907,13 @@
         <v>50</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>20</v>
@@ -6675,10 +6934,10 @@
         <v>70</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F22" s="31" t="n">
         <v>40</v>
@@ -6699,10 +6958,10 @@
         <v>80</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>30</v>
@@ -6711,7 +6970,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6725,10 +6984,10 @@
         <v>85</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>210</v>
@@ -6737,7 +6996,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6748,13 +7007,13 @@
         <v>79</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F25" s="31" t="n">
         <v>10</v>
@@ -6763,7 +7022,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6774,13 +7033,13 @@
         <v>79</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F26" s="31" t="n">
         <v>10</v>
@@ -6789,7 +7048,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6803,10 +7062,10 @@
         <v>70</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F27" s="31" t="n">
         <v>20</v>
@@ -6815,7 +7074,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6856,7 +7115,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -6882,7 +7141,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -6954,10 +7213,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -6978,10 +7237,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -7002,10 +7261,10 @@
         <v>85</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>30</v>
@@ -7026,10 +7285,10 @@
         <v>85</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>90</v>
@@ -7050,10 +7309,10 @@
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>60</v>
@@ -7074,10 +7333,10 @@
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>60</v>
@@ -7098,10 +7357,10 @@
         <v>85</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>30</v>
@@ -7110,7 +7369,7 @@
         <v>2</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7124,10 +7383,10 @@
         <v>85</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>30</v>
@@ -7136,7 +7395,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7150,10 +7409,10 @@
         <v>85</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>30</v>
@@ -7174,10 +7433,10 @@
         <v>89</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>15</v>
@@ -7198,10 +7457,10 @@
         <v>89</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>30</v>
@@ -7222,10 +7481,10 @@
         <v>89</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>15</v>
@@ -7243,13 +7502,13 @@
         <v>50</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>90</v>
@@ -7270,10 +7529,10 @@
         <v>80</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>90</v>
@@ -7282,7 +7541,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7296,10 +7555,10 @@
         <v>85</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>60</v>
@@ -7308,7 +7567,7 @@
         <v>2</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7322,10 +7581,10 @@
         <v>85</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F22" s="31" t="n">
         <v>60</v>
@@ -7334,7 +7593,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7348,10 +7607,10 @@
         <v>89</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>30</v>
@@ -7360,7 +7619,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7371,13 +7630,13 @@
         <v>79</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>15</v>
@@ -7386,7 +7645,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7397,13 +7656,13 @@
         <v>79</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F25" s="31" t="n">
         <v>45</v>
@@ -7451,7 +7710,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -7477,7 +7736,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -7549,10 +7808,10 @@
         <v>80</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F7" s="31" t="n">
         <v>30</v>
@@ -7573,10 +7832,10 @@
         <v>85</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>30</v>
@@ -7597,10 +7856,10 @@
         <v>85</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>120</v>
@@ -7621,10 +7880,10 @@
         <v>85</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F10" s="31" t="n">
         <v>60</v>
@@ -7645,10 +7904,10 @@
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>90</v>
@@ -7669,10 +7928,10 @@
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>60</v>
@@ -7690,13 +7949,13 @@
         <v>50</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>10</v>
@@ -7717,10 +7976,10 @@
         <v>70</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>20</v>
@@ -7729,7 +7988,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7743,10 +8002,10 @@
         <v>80</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>30</v>
@@ -7767,10 +8026,10 @@
         <v>80</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>30</v>
@@ -7791,10 +8050,10 @@
         <v>80</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F17" s="31" t="n">
         <v>30</v>
@@ -7815,10 +8074,10 @@
         <v>85</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F18" s="31" t="n">
         <v>120</v>
@@ -7839,10 +8098,10 @@
         <v>89</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F19" s="31" t="n">
         <v>30</v>
@@ -7860,13 +8119,13 @@
         <v>50</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F20" s="31" t="n">
         <v>45</v>
@@ -7887,10 +8146,10 @@
         <v>80</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F21" s="31" t="n">
         <v>90</v>
@@ -7911,10 +8170,10 @@
         <v>85</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F22" s="31" t="n">
         <v>120</v>
@@ -7935,10 +8194,10 @@
         <v>89</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>45</v>
@@ -7956,13 +8215,13 @@
         <v>79</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>60</v>

--- a/madaporc_suivi_dynamique_plutot.xlsx
+++ b/madaporc_suivi_dynamique_plutot.xlsx
@@ -28,14 +28,14 @@
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="439">
   <si>
     <t xml:space="preserve">MADAPORC — Suivi des tâches &amp; fonctions par membre</t>
   </si>
@@ -1346,6 +1346,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mickaella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chef de Projet</t>
   </si>
   <si>
     <t xml:space="preserve">Noah</t>
@@ -1355,20 +1358,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;- &quot;_€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0&quot; €&quot;_-;\-* #,##0&quot; €&quot;_-;_-* &quot;- €&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0\ %"/>
-    <numFmt numFmtId="170" formatCode="0%"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0"/>
-    <numFmt numFmtId="173" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="174" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="0\ %"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1389,12 +1387,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1560,7 +1552,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="26">
+  <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1584,221 +1576,192 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="8" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" xfId="24" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="24" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Comma" xfId="20"/>
-    <cellStyle name="Comma [0]" xfId="21"/>
-    <cellStyle name="Currency" xfId="22"/>
-    <cellStyle name="Currency [0]" xfId="23"/>
-    <cellStyle name="Normal" xfId="24"/>
-    <cellStyle name="Percent" xfId="25"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -2008,7 +1971,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
@@ -2399,7 +2362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EDBD3C1D-6EC1-4050-90A6-627443F31762}</x14:id>
+          <x14:id>{5C1CA5F2-93AC-468B-A8BE-5B5A73392676}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2415,8 +2378,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EDBD3C1D-6EC1-4050-90A6-627443F31762}">
-            <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="true">
+          <x14:cfRule type="dataBar" id="{5C1CA5F2-93AC-468B-A8BE-5B5A73392676}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:negativeFillColor rgb="FFC2410C"/>
@@ -2437,7 +2400,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.44"/>
@@ -2775,7 +2738,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
@@ -2803,7 +2766,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="str">
         <f aca="false">"Durée totale estimée : "&amp;TEXT(SUM($G$5:$G$18)/60,"0.0")&amp;" h"&amp;"   ·   Heures faites : "&amp;TEXT((SUMIF($E$5:$E$18,"Terminé",$G$5:$G$18)+0.5*SUMIF($E$5:$E$18,"En cours",$G$5:$G$18))/60,"0.0")&amp;" h"&amp;"   ·   Heures restantes : "&amp;TEXT((SUMIF($E$5:$E$18,"Pas fini",$G$5:$G$18)+0.5*SUMIF($E$5:$E$18,"En cours",$G$5:$G$18))/60,"0.0")&amp;" h"</f>
         <v>Durée totale estimée : 13,0 h   ·   Heures faites : 2,5 h   ·   Heures restantes : 10,5 h</v>
@@ -3149,7 +3112,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F19" s="33" t="s">
         <v>94</v>
       </c>
@@ -3158,14 +3121,14 @@
         <v>780</v>
       </c>
     </row>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
@@ -3194,7 +3157,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="C2:G11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="40" width="30.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="40" width="32.82"/>
@@ -3202,7 +3165,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="40" width="23.29"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C2" s="40" t="s">
         <v>405</v>
       </c>
@@ -3219,7 +3182,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C3" s="40" t="s">
         <v>410</v>
       </c>
@@ -3236,7 +3199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C4" s="40" t="s">
         <v>413</v>
       </c>
@@ -3246,14 +3209,14 @@
       <c r="E4" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="41" t="s">
         <v>415</v>
       </c>
       <c r="G4" s="41" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C5" s="40" t="s">
         <v>416</v>
       </c>
@@ -3263,14 +3226,14 @@
       <c r="E5" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="41" t="s">
         <v>417</v>
       </c>
       <c r="G5" s="41" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C6" s="40" t="s">
         <v>418</v>
       </c>
@@ -3287,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C7" s="40" t="s">
         <v>419</v>
       </c>
@@ -3297,14 +3260,14 @@
       <c r="E7" s="42" t="n">
         <v>46193</v>
       </c>
-      <c r="F7" s="43" t="s">
+      <c r="F7" s="41" t="s">
         <v>417</v>
       </c>
       <c r="G7" s="41" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C8" s="40" t="s">
         <v>420</v>
       </c>
@@ -3321,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C9" s="40" t="s">
         <v>422</v>
       </c>
@@ -3331,14 +3294,14 @@
       <c r="E9" s="42" t="n">
         <v>46207</v>
       </c>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="41" t="s">
         <v>417</v>
       </c>
       <c r="G9" s="41" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C10" s="40" t="s">
         <v>423</v>
       </c>
@@ -3348,14 +3311,14 @@
       <c r="E10" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="41" t="s">
         <v>417</v>
       </c>
       <c r="G10" s="41" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="40" t="s">
         <v>424</v>
       </c>
@@ -3365,7 +3328,7 @@
       <c r="E11" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="41" t="s">
         <v>415</v>
       </c>
       <c r="G11" s="41" t="n">
@@ -3377,8 +3340,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3389,212 +3352,205 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="40" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="40" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="40" width="14.19"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="40" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="40" t="s">
         <v>426</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="40" t="s">
         <v>427</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="40" t="s">
         <v>428</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="40" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="40" t="s">
         <v>431</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="40" t="n">
         <v>440</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="40" t="n">
         <v>7.33</v>
       </c>
-      <c r="E2" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F2" s="44" t="n">
+      <c r="E2" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F2" s="43" t="n">
         <f aca="false">(C2/60)*E2</f>
-        <v>62333.3333333333</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+        <v>146666.666666667</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="B3" s="0" t="str">
-        <f aca="false">B2</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3" s="40" t="n">
         <v>995</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="40" t="n">
         <v>16.33</v>
       </c>
-      <c r="E3" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F3" s="44" t="n">
+      <c r="E3" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F3" s="43" t="n">
         <f aca="false">(C3/60)*E3</f>
-        <v>140958.333333333</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+        <v>331666.666666667</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="s">
         <v>433</v>
       </c>
-      <c r="B4" s="0" t="str">
-        <f aca="false">B3</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="B4" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="40" t="n">
         <v>1400</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="40" t="n">
         <v>23.33</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F4" s="44" t="n">
+      <c r="E4" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F4" s="43" t="n">
         <f aca="false">(C4/60)*E4</f>
-        <v>198333.333333333</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+        <v>466666.666666667</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="40" t="s">
         <v>434</v>
       </c>
-      <c r="B5" s="0" t="str">
-        <f aca="false">B4</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="40" t="n">
         <v>750</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="40" t="n">
         <v>12.5</v>
       </c>
-      <c r="E5" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F5" s="44" t="n">
+      <c r="E5" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F5" s="43" t="n">
         <f aca="false">(C5/60)*E5</f>
-        <v>106250</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="40" t="s">
         <v>435</v>
       </c>
-      <c r="B6" s="0" t="str">
-        <f aca="false">B5</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="40" t="n">
         <v>990</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="40" t="n">
         <v>16.5</v>
       </c>
-      <c r="E6" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F6" s="44" t="n">
+      <c r="E6" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="43" t="n">
         <f aca="false">(C6/60)*E6</f>
-        <v>140250</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
         <v>436</v>
       </c>
-      <c r="B7" s="0" t="str">
-        <f aca="false">B6</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="40" t="s">
+        <v>437</v>
+      </c>
+      <c r="C7" s="40" t="n">
         <v>760</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="40" t="n">
         <v>12.67</v>
       </c>
-      <c r="E7" s="0" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F7" s="44" t="n">
+      <c r="E7" s="40" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F7" s="43" t="n">
         <f aca="false">(C7/60)*E7</f>
-        <v>380000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+        <v>316666.666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="40" t="s">
         <v>423</v>
       </c>
-      <c r="B8" s="0" t="str">
-        <f aca="false">B7</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C8" s="40" t="n">
         <v>840</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="40" t="n">
         <v>14</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F8" s="44" t="n">
+      <c r="E8" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F8" s="43" t="n">
         <f aca="false">(C8/60)*E8</f>
-        <v>119000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="B9" s="0" t="str">
-        <f aca="false">B8</f>
-        <v>Dev Junior</v>
-      </c>
-      <c r="C9" s="0" t="n">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="40" t="s">
+        <v>438</v>
+      </c>
+      <c r="B9" s="40" t="s">
+        <v>432</v>
+      </c>
+      <c r="C9" s="40" t="n">
         <v>1020</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="40" t="n">
         <v>17</v>
       </c>
-      <c r="E9" s="0" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F9" s="44" t="n">
+      <c r="E9" s="40" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F9" s="43" t="n">
         <f aca="false">(C9/60)*E9</f>
-        <v>144500</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="44" t="n">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F10" s="43" t="n">
         <f aca="false">SUM(F2:F9)</f>
-        <v>1291625</v>
+        <v>2461666.66666667</v>
       </c>
     </row>
   </sheetData>
@@ -3602,8 +3558,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -3614,7 +3570,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -4171,7 +4127,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -4850,7 +4806,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -5465,7 +5421,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -5902,7 +5858,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -6459,7 +6415,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -7115,7 +7071,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
@@ -7710,7 +7666,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
